--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_303_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_303_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M2" t="n">
         <v>4</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>8</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>3</v>
@@ -1531,7 +1531,7 @@
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
         <v>15</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X20" t="n">
         <v>2</v>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
@@ -2511,16 +2511,16 @@
         <v>16</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2906,13 +2906,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>2</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>132</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X30" t="n">
         <v>16</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>1</v>
@@ -4684,16 +4684,16 @@
         <v>7</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>2</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -5076,10 +5076,10 @@
         <v>8</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5670,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X42" t="n">
         <v>5</v>
@@ -5860,10 +5860,10 @@
         <v>9</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6059,13 +6059,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>3</v>
@@ -6784,16 +6784,16 @@
         <v>95</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X48" t="n">
         <v>19</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_303_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_303_EL.xlsx
@@ -674,10 +674,10 @@
         <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P2" t="n">
         <v>12</v>
@@ -833,10 +833,10 @@
         <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P3" t="n">
         <v>8</v>
@@ -1347,10 +1347,10 @@
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,10 +1935,10 @@
         <v>3</v>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -3307,10 +3307,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3839,10 +3839,10 @@
         <v>7</v>
       </c>
       <c r="X30" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Y30" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -4696,14 +4696,14 @@
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5088,14 +5088,14 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5676,10 +5676,10 @@
         <v>2</v>
       </c>
       <c r="X42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -6460,14 +6460,14 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,10 +6796,10 @@
         <v>7</v>
       </c>
       <c r="X48" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="Y48" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
